--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD93A66F-251B-4B19-89B7-299E06C4B06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DB77D8-5A73-4928-965A-98C2497E4C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -595,6 +595,7 @@
       <c r="A19">
         <v>17</v>
       </c>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DB77D8-5A73-4928-965A-98C2497E4C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FDD32C-5C27-490A-B96D-8CB69A723505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -122,6 +122,30 @@
     <rPh sb="26" eb="28">
       <t>ガゾウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isInputPlayerNameFieldStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>showSystemMessageNumber</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isPlaySoundNoiseStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isShowTalkMessageStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ShowTalkMessageNumber</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>isTutorialStatus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -450,214 +474,526 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="73.25" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="26.625" customWidth="1"/>
+    <col min="5" max="5" width="22.25" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
+    <col min="7" max="7" width="24.125" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="37.5">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>38</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="37.5">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="37.5">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>43</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>44</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="37.5">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>46</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="37.5">
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>47</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>49</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FDD32C-5C27-490A-B96D-8CB69A723505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFD9B32-4E72-4BA0-B7C1-CF7E4842C211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,13 +36,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>message</t>
   </si>
   <si>
     <t>破棄します</t>
@@ -146,6 +143,79 @@
   </si>
   <si>
     <t>isTutorialStatus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeJapanese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>message</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Press P, Z, or ESC to open the pause screen → "Item Check"
+→ "Document" → "Tutorial"</t>
+  </si>
+  <si>
+    <t>Left-click... Obtain a mystery item.</t>
+  </si>
+  <si>
+    <t>Press P, Z, or ESC to open the pause screen → "Item Check"
+→ "Mystery Item" → "Hammer" or "Rope"</t>
+  </si>
+  <si>
+    <t>Left-click... touch the blue orb of judgment.
+Left-click the mystery item image to select it.</t>
+  </si>
+  <si>
+    <t>This is the Eternal Realm.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Please tell me the name you used in the living world.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enter a name between 2 and 10 characters.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Thank you for telling me.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>And now... I shall take that name and…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Discard it.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Starting Tutorial.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Move the player and
+left-click to obtain the document.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tutorial complete.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeEnglish</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The world where those who have died 
+in the living world eventually arrive.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -189,10 +259,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,54 +550,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="73.25" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="26.625" customWidth="1"/>
-    <col min="5" max="5" width="22.25" customWidth="1"/>
-    <col min="6" max="6" width="23.875" customWidth="1"/>
-    <col min="7" max="7" width="24.125" customWidth="1"/>
-    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="63.625" customWidth="1"/>
+    <col min="5" max="5" width="20.25" customWidth="1"/>
+    <col min="6" max="6" width="27.25" customWidth="1"/>
+    <col min="7" max="7" width="26.625" customWidth="1"/>
+    <col min="8" max="8" width="22.25" customWidth="1"/>
+    <col min="9" max="9" width="23.875" customWidth="1"/>
+    <col min="10" max="10" width="24.125" customWidth="1"/>
+    <col min="11" max="11" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2">
         <v>0</v>
       </c>
@@ -534,22 +620,31 @@
       <c r="H2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -560,22 +655,31 @@
       <c r="H3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -586,74 +690,101 @@
       <c r="H4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>32</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="G6">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -664,48 +795,66 @@
       <c r="H7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E8">
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -716,17 +865,24 @@
       <c r="H9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
+      <c r="D10" s="2"/>
       <c r="E10">
         <v>0</v>
       </c>
@@ -739,153 +895,181 @@
       <c r="H10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>1</v>
       </c>
-      <c r="G11">
+      <c r="J11">
         <v>38</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="37.5">
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="37.5">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1"/>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <v>43</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="37.5">
+    <row r="13" spans="1:11" ht="37.5">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="1"/>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <v>44</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="1"/>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>46</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="37.5">
+    <row r="15" spans="1:11" ht="37.5">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="1"/>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
         <v>47</v>
       </c>
-      <c r="H15">
+      <c r="K15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="37.5">
+    <row r="16" spans="1:11" ht="37.5">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="F16">
         <v>0</v>
       </c>
@@ -893,107 +1077,124 @@
         <v>0</v>
       </c>
       <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="1"/>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>2</v>
       </c>
-      <c r="G17">
+      <c r="J17">
         <v>49</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFD9B32-4E72-4BA0-B7C1-CF7E4842C211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E665FE-1528-42BF-B539-BCCC2E47EE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,10 +173,6 @@
 Left-click the mystery item image to select it.</t>
   </si>
   <si>
-    <t>This is the Eternal Realm.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Please tell me the name you used in the living world.</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -216,6 +212,10 @@
   <si>
     <t>The world where those who have died 
 in the living world eventually arrive.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>This is the eternal world.</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -579,7 +579,7 @@
         <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s">
         <v>15</v>
@@ -641,7 +641,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -676,7 +676,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -711,7 +711,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -746,7 +746,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>32</v>
@@ -781,7 +781,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>32</v>
@@ -816,7 +816,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8">
         <v>32</v>
@@ -851,7 +851,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>32</v>
@@ -912,8 +912,14 @@
       <c r="B11" t="s">
         <v>7</v>
       </c>
+      <c r="C11" s="1">
+        <v>22</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="E11" s="1">
+        <v>22</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -941,11 +947,15 @@
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>22</v>
+      </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="E12" s="1">
+        <v>22</v>
+      </c>
       <c r="F12">
         <v>0</v>
       </c>
@@ -972,11 +982,15 @@
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1">
+        <v>22</v>
+      </c>
       <c r="D13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1">
+        <v>22</v>
+      </c>
       <c r="F13">
         <v>0</v>
       </c>
@@ -1003,11 +1017,15 @@
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>22</v>
+      </c>
       <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1">
+        <v>22</v>
+      </c>
       <c r="F14">
         <v>0</v>
       </c>
@@ -1034,11 +1052,15 @@
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>22</v>
+      </c>
       <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <v>22</v>
+      </c>
       <c r="F15">
         <v>0</v>
       </c>
@@ -1065,11 +1087,15 @@
       <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>22</v>
+      </c>
       <c r="D16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="1">
+        <v>22</v>
+      </c>
       <c r="F16">
         <v>0</v>
       </c>
@@ -1096,11 +1122,15 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>22</v>
+      </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="E17" s="1">
+        <v>22</v>
+      </c>
       <c r="F17">
         <v>0</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E665FE-1528-42BF-B539-BCCC2E47EE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1B3DED-3EB0-4265-9D80-78D3AC0BA335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,18 +92,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーを動かして
-左クリックでドキュメント入手</t>
-    <rPh sb="6" eb="7">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左クリック…ミステリーアイテム入手</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>P or Z or ESCキーでポーズ画面を開く→「アイテム確認」
 →「ドキュメント」→「チュートリアル」</t>
     <phoneticPr fontId="1"/>
@@ -162,9 +150,6 @@
 → "Document" → "Tutorial"</t>
   </si>
   <si>
-    <t>Left-click... Obtain a mystery item.</t>
-  </si>
-  <si>
     <t>Press P, Z, or ESC to open the pause screen → "Item Check"
 → "Mystery Item" → "Hammer" or "Rope"</t>
   </si>
@@ -197,11 +182,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Move the player and
-left-click to obtain the document.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Tutorial complete.</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -216,6 +196,27 @@
   </si>
   <si>
     <t>This is the eternal world.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Move the player and
+left-click to open the drawer.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーを動かして
+左クリックで引き出しを開ける</t>
+    <rPh sb="6" eb="7">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Left-click... Open the drawer.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左クリック…引き出しを開ける</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -570,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
-        <v>23</v>
-      </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -641,7 +642,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -676,7 +677,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -711,7 +712,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -746,7 +747,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>32</v>
@@ -781,7 +782,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>32</v>
@@ -816,7 +817,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>32</v>
@@ -851,7 +852,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>32</v>
@@ -916,7 +917,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
         <v>22</v>
@@ -945,13 +946,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1">
         <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1">
         <v>22</v>
@@ -980,13 +981,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
         <v>22</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1">
         <v>22</v>
@@ -1015,13 +1016,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1">
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1">
         <v>22</v>
@@ -1050,13 +1051,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" s="1">
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1">
         <v>22</v>
@@ -1085,13 +1086,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1">
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E16" s="1">
         <v>22</v>
@@ -1126,7 +1127,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1">
         <v>22</v>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1B3DED-3EB0-4265-9D80-78D3AC0BA335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55E7C61-2586-4F2A-A653-1E8E7C53EC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,74 +42,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>破棄します</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ここは常世</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現世で亡くなった者が行きつく世界です</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなたが現世で使用していた名前を教えて下さい</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>教えていただきありがとうございます</t>
-    <rPh sb="0" eb="1">
-      <t>オシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>それでは　今からあなたの名前をここで…</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チュートリアルを開始します</t>
-  </si>
-  <si>
-    <t>　チュートリアルを終了します</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2文字以上10文字以内で入力してください</t>
-    <rPh sb="1" eb="5">
-      <t>モジイジョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>P or Z or ESCキーでポーズ画面を開く→「アイテム確認」
-→「ドキュメント」→「チュートリアル」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>P or Z or ESCキーでポーズ画面を開く→「アイテム確認」
-→「ミステリーアイテム」→「ハンマー」または 「ロープ」</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左クリック…裁きの青玉に触れる
-ミステリーアイテムの画像を左クリックで選択</t>
-    <rPh sb="26" eb="28">
-      <t>ガゾウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>isInputPlayerNameFieldStatus</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -204,19 +136,88 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーを動かして
-左クリックで引き出しを開ける</t>
-    <rPh sb="6" eb="7">
-      <t>ウゴ</t>
+    <t>Left-click... Open the drawer.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ここは&lt;r="とこよ"&gt;常世&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="うつしよ"&gt;現世&lt;/r&gt;で&lt;r="な"&gt;亡&lt;/r&gt;くなった&lt;r="もの"&gt;者&lt;/r&gt;が&lt;r="い"&gt;行&lt;/r&gt;きつく&lt;r="せかい"&gt;世界&lt;/r&gt;です</t>
+    <rPh sb="10" eb="12">
+      <t>ウツシヨ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Left-click... Open the drawer.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>左クリック…引き出しを開ける</t>
+    <rPh sb="24" eb="25">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>セカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="おし"&gt;教&lt;/r&gt;えていただきありがとうございます</t>
+    <rPh sb="8" eb="9">
+      <t>キョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2&lt;r="もじ"&gt;文字&lt;/r&gt;&lt;r="いじょう"&gt;以上&lt;/r&gt;10&lt;r="もじ"&gt;文字&lt;/r&gt;&lt;r="いない"&gt;以内&lt;/r&gt;で&lt;r="にゅうりょく"&gt;入力&lt;/r&gt;してください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたが&lt;r="うつしよ"&gt;現世&lt;/r&gt;で&lt;r="しよう"&gt;使用&lt;/r&gt;していた&lt;r="なまえ"&gt;名前&lt;/r&gt;を&lt;r="おし"&gt;教&lt;/r&gt;えて&lt;r="くだ"&gt;下&lt;/r&gt;さい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それでは　今からあなたの&lt;r="なまえ"&gt;名前&lt;/r&gt;をここで…</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="はき"&gt;破棄&lt;/r&gt;します</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアルを&lt;r="かいし"&gt;開始&lt;/r&gt;します</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーを&lt;r="うご"&gt;動&lt;/r&gt;かして
+&lt;r="ひだり"&gt;左&lt;/r&gt;クリックで&lt;r="ひ"&gt;引&lt;/r&gt;き&lt;r="だ"&gt;出&lt;/r&gt;しを&lt;r="あ"&gt;開&lt;/r&gt;ける</t>
+    <rPh sb="14" eb="15">
+      <t>ドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P or Z or ESCキーでポーズ&lt;r="がめん"&gt;画面&lt;/r&gt;を&lt;r="ひら"&gt;開&lt;/r&gt;く→「アイテム&lt;r="かくにん"&gt;確認&lt;/r&gt;」
+→「ドキュメント」→「チュートリアル」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ひだり"&gt;左&lt;/r&gt;クリック…&lt;r="ひ"&gt;引&lt;/r&gt;き&lt;r="だ"&gt;出&lt;/r&gt;しを&lt;r="あ"&gt;開&lt;/r&gt;ける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P or Z or ESCキーでポーズ&lt;r="がめん"&gt;画面&lt;/r&gt;を&lt;r="ひら"&gt;開&lt;/r&gt;く→「アイテム&lt;r="かくにん"&gt;確認&lt;/r&gt;」
+→「ミステリーアイテム」→「ハンマー」または 「ロープ」</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;r="ひだり"&gt;左&lt;/r&gt;クリック…&lt;r="さば"&gt;裁&lt;/r&gt;きの&lt;r="せいぎょく"&gt;青玉&lt;/r&gt;に&lt;r="ふ"&gt;触&lt;/r&gt;れる
+ミステリーアイテムの&lt;r="がぞう"&gt;画像&lt;/r&gt;を&lt;r="ひだり"&gt;左&lt;/r&gt;クリックで&lt;r="せんたく"&gt;選択&lt;/r&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　チュートリアルを&lt;r="しゅうりょう"&gt;終了&lt;/r&gt;します</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -554,7 +555,7 @@
   <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="73.25" customWidth="1"/>
+    <col min="2" max="2" width="114.5" customWidth="1"/>
     <col min="3" max="3" width="20.25" customWidth="1"/>
     <col min="4" max="4" width="63.625" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
@@ -571,34 +572,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>32</v>
-      </c>
       <c r="F1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -636,13 +637,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -671,13 +672,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>32</v>
@@ -701,18 +702,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -736,18 +737,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>32</v>
@@ -775,14 +776,14 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>32</v>
@@ -811,13 +812,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>32</v>
@@ -846,13 +847,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>32</v>
@@ -911,13 +912,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
         <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1">
         <v>22</v>
@@ -946,13 +947,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E12" s="1">
         <v>22</v>
@@ -981,13 +982,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C13" s="1">
-        <v>22</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="E13" s="1">
         <v>22</v>
@@ -1016,13 +1017,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1">
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E14" s="1">
         <v>22</v>
@@ -1051,13 +1052,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C15" s="1">
-        <v>22</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E15" s="1">
         <v>22</v>
@@ -1086,13 +1087,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="1">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C16" s="1">
-        <v>22</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="E16" s="1">
         <v>22</v>
@@ -1121,13 +1122,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1">
         <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1">
         <v>22</v>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55E7C61-2586-4F2A-A653-1E8E7C53EC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCE0651-4F1B-4074-B112-E19562578DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -220,12 +220,66 @@
     <t>　チュートリアルを&lt;r="しゅうりょう"&gt;終了&lt;/r&gt;します</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>这里是常世</t>
+  </si>
+  <si>
+    <t>这是现世逝去之人最终到达的世界</t>
+  </si>
+  <si>
+    <t>请告诉我你在现世使用的名字</t>
+  </si>
+  <si>
+    <t>请输入2个字以上10个字以内的名字</t>
+  </si>
+  <si>
+    <t>感谢你告诉我</t>
+  </si>
+  <si>
+    <t>那么　现在就在这里将你的名字…</t>
+  </si>
+  <si>
+    <t>舍弃</t>
+  </si>
+  <si>
+    <t>开始教程</t>
+  </si>
+  <si>
+    <t>移动角色
+用鼠标左键打开抽屉</t>
+  </si>
+  <si>
+    <t>按 P、Z 或 ESC 键打开暂停画面→「物品确认」
+→「文件」→「教程」</t>
+  </si>
+  <si>
+    <t>鼠标左键…打开抽屉</t>
+  </si>
+  <si>
+    <t>按 P、Z 或 ESC 键打开暂停画面→「物品确认」
+→「神秘物品」→「锤子」或「绳子」</t>
+  </si>
+  <si>
+    <t>鼠标左键…触碰裁决之蓝玉
+用鼠标左键点击神秘物品图像进行选择</t>
+  </si>
+  <si>
+    <t>　结束教程</t>
+  </si>
+  <si>
+    <t>messageChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese01</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +293,12 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -261,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -271,6 +331,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,22 +616,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
     <col min="3" max="3" width="20.25" customWidth="1"/>
     <col min="4" max="4" width="63.625" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
-    <col min="6" max="6" width="27.25" customWidth="1"/>
+    <col min="6" max="6" width="38.125" customWidth="1"/>
     <col min="7" max="7" width="26.625" customWidth="1"/>
-    <col min="8" max="8" width="22.25" customWidth="1"/>
-    <col min="9" max="9" width="23.875" customWidth="1"/>
-    <col min="10" max="10" width="24.125" customWidth="1"/>
-    <col min="11" max="11" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="27.25" customWidth="1"/>
+    <col min="9" max="9" width="26.625" customWidth="1"/>
+    <col min="10" max="10" width="22.25" customWidth="1"/>
+    <col min="11" max="11" width="23.875" customWidth="1"/>
+    <col min="12" max="12" width="24.125" customWidth="1"/>
+    <col min="13" max="13" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -584,25 +650,31 @@
         <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>0</v>
       </c>
@@ -613,12 +685,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
         <v>0</v>
       </c>
@@ -631,8 +697,14 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>1</v>
       </c>
@@ -648,11 +720,11 @@
       <c r="E3">
         <v>32</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+      <c r="F3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="4">
+        <v>32</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -666,8 +738,14 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="37.5">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -683,11 +761,11 @@
       <c r="E4">
         <v>32</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4">
+        <v>32</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -701,8 +779,14 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="37.5">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="67.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -718,15 +802,15 @@
       <c r="E5">
         <v>32</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="4">
+        <v>32</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
         <v>0</v>
       </c>
@@ -736,8 +820,14 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="37.5">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="67.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -753,26 +843,32 @@
       <c r="E6">
         <v>32</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="4">
+        <v>32</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="34.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -788,11 +884,11 @@
       <c r="E7">
         <v>32</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
+      <c r="F7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="4">
+        <v>32</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -806,8 +902,14 @@
       <c r="K7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>6</v>
       </c>
@@ -823,26 +925,32 @@
       <c r="E8">
         <v>32</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+      <c r="F8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="4">
+        <v>32</v>
       </c>
       <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>3</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>7</v>
       </c>
@@ -858,11 +966,11 @@
       <c r="E9">
         <v>32</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+      <c r="F9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="4">
+        <v>32</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -876,8 +984,14 @@
       <c r="K9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>8</v>
       </c>
@@ -888,12 +1002,6 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
         <v>0</v>
       </c>
@@ -906,8 +1014,14 @@
       <c r="K10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>9</v>
       </c>
@@ -923,26 +1037,32 @@
       <c r="E11" s="1">
         <v>22</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+      <c r="F11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="5">
+        <v>22</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>1</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>38</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="37.5">
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="67.5">
       <c r="A12">
         <v>10</v>
       </c>
@@ -958,11 +1078,11 @@
       <c r="E12" s="1">
         <v>22</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+      <c r="F12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="5">
+        <v>22</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -971,13 +1091,19 @@
         <v>0</v>
       </c>
       <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <v>43</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="37.5">
+    <row r="13" spans="1:13" ht="150">
       <c r="A13">
         <v>11</v>
       </c>
@@ -993,11 +1119,11 @@
       <c r="E13" s="1">
         <v>22</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
+      <c r="F13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="5">
+        <v>22</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1006,13 +1132,19 @@
         <v>0</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
         <v>44</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13" ht="51">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1028,11 +1160,11 @@
       <c r="E14" s="1">
         <v>22</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
+      <c r="F14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="5">
+        <v>22</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1041,13 +1173,19 @@
         <v>0</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>46</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="37.5">
+    <row r="15" spans="1:13" ht="183">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1063,11 +1201,11 @@
       <c r="E15" s="1">
         <v>22</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
+      <c r="F15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="5">
+        <v>22</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1076,13 +1214,19 @@
         <v>0</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
         <v>47</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="37.5">
+    <row r="16" spans="1:13" ht="133.5">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1098,11 +1242,11 @@
       <c r="E16" s="1">
         <v>22</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
+      <c r="F16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="5">
+        <v>22</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1114,10 +1258,16 @@
         <v>0</v>
       </c>
       <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:13" ht="34.5">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1133,31 +1283,37 @@
       <c r="E17" s="1">
         <v>22</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
+      <c r="F17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="5">
+        <v>22</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>2</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>49</v>
       </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1166,67 +1322,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:13">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:13">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:13">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:13">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:13">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:13">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:13">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:13">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:13">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCE0651-4F1B-4074-B112-E19562578DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE8F62E-3CA7-4B39-AA88-C54D1BC1AA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -274,12 +274,66 @@
     <t>messageSizeChinese01</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>這裡是常世</t>
+  </si>
+  <si>
+    <t>這是現世逝去之人最終到達的世界</t>
+  </si>
+  <si>
+    <t>請告訴我你在現世使用的名字</t>
+  </si>
+  <si>
+    <t>請輸入2個字以上10個字以內的名字</t>
+  </si>
+  <si>
+    <t>感謝你告訴我</t>
+  </si>
+  <si>
+    <t>那麼　現在就在這裡將你的名字…</t>
+  </si>
+  <si>
+    <t>捨棄</t>
+  </si>
+  <si>
+    <t>開始教程</t>
+  </si>
+  <si>
+    <t>移動角色
+用滑鼠左鍵開啟抽屜</t>
+  </si>
+  <si>
+    <t>按 P、Z 或 ESC 鍵開啟暫停畫面→「物品確認」
+→「檔案」→「教程」</t>
+  </si>
+  <si>
+    <t>滑鼠左鍵…開啟抽屜</t>
+  </si>
+  <si>
+    <t>按 P、Z 或 ESC 鍵開啟暫停畫面→「物品確認」
+→「神秘物品」→「錘子」或「繩子」</t>
+  </si>
+  <si>
+    <t>滑鼠左鍵…觸碰裁決之藍玉
+用滑鼠左鍵點選神秘物品影象進行選擇</t>
+  </si>
+  <si>
+    <t>　結束教程</t>
+  </si>
+  <si>
+    <t>messageChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSizeChinese02</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +353,12 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -321,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -334,6 +394,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -624,16 +689,16 @@
     <col min="4" max="4" width="63.625" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
     <col min="6" max="6" width="38.125" customWidth="1"/>
-    <col min="7" max="7" width="26.625" customWidth="1"/>
-    <col min="8" max="8" width="27.25" customWidth="1"/>
-    <col min="9" max="9" width="26.625" customWidth="1"/>
-    <col min="10" max="10" width="22.25" customWidth="1"/>
-    <col min="11" max="11" width="23.875" customWidth="1"/>
-    <col min="12" max="12" width="24.125" customWidth="1"/>
-    <col min="13" max="13" width="14.625" customWidth="1"/>
+    <col min="7" max="9" width="26.625" customWidth="1"/>
+    <col min="10" max="10" width="27.25" customWidth="1"/>
+    <col min="11" max="11" width="26.625" customWidth="1"/>
+    <col min="12" max="12" width="22.25" customWidth="1"/>
+    <col min="13" max="13" width="23.875" customWidth="1"/>
+    <col min="14" max="14" width="24.125" customWidth="1"/>
+    <col min="15" max="15" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -655,26 +720,32 @@
       <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -685,12 +756,8 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
       <c r="J2">
         <v>0</v>
       </c>
@@ -703,8 +770,14 @@
       <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -726,11 +799,11 @@
       <c r="G3" s="4">
         <v>32</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
+      <c r="H3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="7">
+        <v>32</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -744,8 +817,14 @@
       <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="37.5">
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -767,11 +846,11 @@
       <c r="G4" s="4">
         <v>32</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
+      <c r="H4" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="7">
+        <v>32</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -785,8 +864,14 @@
       <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="67.5">
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -808,15 +893,15 @@
       <c r="G5" s="4">
         <v>32</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="7">
+        <v>32</v>
+      </c>
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
       <c r="K5">
         <v>0</v>
       </c>
@@ -826,8 +911,14 @@
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="67.5">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -849,26 +940,32 @@
       <c r="G6" s="4">
         <v>32</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="7">
+        <v>32</v>
+      </c>
+      <c r="J6">
         <v>2</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="34.5">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -890,11 +987,11 @@
       <c r="G7" s="4">
         <v>32</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
+      <c r="H7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="7">
+        <v>32</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -908,8 +1005,14 @@
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -931,26 +1034,32 @@
       <c r="G8" s="4">
         <v>32</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
+      <c r="H8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="7">
+        <v>32</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>3</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
       <c r="M8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -972,11 +1081,11 @@
       <c r="G9" s="4">
         <v>32</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
+      <c r="H9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="7">
+        <v>32</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -990,8 +1099,14 @@
       <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1002,12 +1117,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
       <c r="J10">
         <v>0</v>
       </c>
@@ -1020,8 +1131,14 @@
       <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1043,26 +1160,32 @@
       <c r="G11" s="5">
         <v>22</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+      <c r="H11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="8">
+        <v>22</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>1</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>38</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="67.5">
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="37.5">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1084,11 +1207,11 @@
       <c r="G12" s="5">
         <v>22</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+      <c r="H12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="8">
+        <v>22</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1097,13 +1220,19 @@
         <v>0</v>
       </c>
       <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
         <v>43</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="150">
+    <row r="13" spans="1:15" ht="51">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1125,11 +1254,11 @@
       <c r="G13" s="5">
         <v>22</v>
       </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+      <c r="H13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="8">
+        <v>22</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1138,13 +1267,19 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>44</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="51">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1166,11 +1301,11 @@
       <c r="G14" s="5">
         <v>22</v>
       </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
+      <c r="H14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="8">
+        <v>22</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1179,13 +1314,19 @@
         <v>0</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
         <v>46</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="183">
+    <row r="15" spans="1:15" ht="62.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1207,11 +1348,11 @@
       <c r="G15" s="5">
         <v>22</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
+      <c r="H15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="8">
+        <v>22</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1220,13 +1361,19 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
         <v>47</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="133.5">
+    <row r="16" spans="1:15" ht="47.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1248,11 +1395,11 @@
       <c r="G16" s="5">
         <v>22</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
+      <c r="H16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="8">
+        <v>22</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1264,10 +1411,16 @@
         <v>0</v>
       </c>
       <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="34.5">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1289,31 +1442,37 @@
       <c r="G17" s="5">
         <v>22</v>
       </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
+      <c r="H17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="8">
+        <v>22</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>2</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>49</v>
       </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1322,67 +1481,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:15">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:15">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:15">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:15">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:15">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE8F62E-3CA7-4B39-AA88-C54D1BC1AA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81081E91-609E-4695-9AD5-B782AE314735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -327,6 +327,58 @@
   <si>
     <t>messageSizeChinese02</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageSpanish</t>
+  </si>
+  <si>
+    <t>messageSizeSpanish</t>
+  </si>
+  <si>
+    <t>Este es el mundo eterno.</t>
+  </si>
+  <si>
+    <t>Es el mundo al que llegan quienes mueren en el mundo de los vivos.</t>
+  </si>
+  <si>
+    <t>Dime el nombre que usabas en el mundo de los vivos.</t>
+  </si>
+  <si>
+    <t>Introduce un nombre de entre 2 y 10 caracteres.</t>
+  </si>
+  <si>
+    <t>Gracias por decírmelo.</t>
+  </si>
+  <si>
+    <t>Bien, ahora mismo tu nombre...</t>
+  </si>
+  <si>
+    <t>será descartado.</t>
+  </si>
+  <si>
+    <t>Iniciando el tutorial.</t>
+  </si>
+  <si>
+    <t>Mueve al personaje
+y haz clic izquierdo para abrir el cajón.</t>
+  </si>
+  <si>
+    <t>Pulsa P, Z o ESC para abrir la pantalla de pausa → «Revisar objetos»
+→ «Documento» → «Tutorial»</t>
+  </si>
+  <si>
+    <t>Clic izquierdo... abrir el cajón.</t>
+  </si>
+  <si>
+    <t>Pulsa P, Z o ESC para abrir la pantalla de pausa → «Revisar objetos»
+→ «Objeto Misterioso» → «Martillo» o «Cuerda»</t>
+  </si>
+  <si>
+    <t>Clic izquierdo... tocar la Esfera Azul del Juicio.
+Haz clic izquierdo en la imagen del Objeto Misterioso para seleccionarlo.</t>
+  </si>
+  <si>
+    <t>Finalizando el tutorial.</t>
   </si>
 </sst>
 </file>
@@ -381,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -396,10 +448,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -689,16 +750,16 @@
     <col min="4" max="4" width="63.625" customWidth="1"/>
     <col min="5" max="5" width="20.25" customWidth="1"/>
     <col min="6" max="6" width="38.125" customWidth="1"/>
-    <col min="7" max="9" width="26.625" customWidth="1"/>
-    <col min="10" max="10" width="27.25" customWidth="1"/>
-    <col min="11" max="11" width="26.625" customWidth="1"/>
-    <col min="12" max="12" width="22.25" customWidth="1"/>
-    <col min="13" max="13" width="23.875" customWidth="1"/>
-    <col min="14" max="14" width="24.125" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
+    <col min="7" max="11" width="26.625" customWidth="1"/>
+    <col min="12" max="12" width="27.25" customWidth="1"/>
+    <col min="13" max="13" width="26.625" customWidth="1"/>
+    <col min="14" max="14" width="22.25" customWidth="1"/>
+    <col min="15" max="15" width="23.875" customWidth="1"/>
+    <col min="16" max="16" width="24.125" customWidth="1"/>
+    <col min="17" max="17" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -720,32 +781,38 @@
       <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" t="s">
         <v>70</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>0</v>
       </c>
@@ -756,14 +823,8 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
       <c r="L2">
         <v>0</v>
       </c>
@@ -776,8 +837,14 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -799,17 +866,17 @@
       <c r="G3" s="4">
         <v>32</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="7">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
+      <c r="I3" s="6">
+        <v>32</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="8">
+        <v>32</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -823,8 +890,14 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="37.5">
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -846,17 +919,17 @@
       <c r="G4" s="4">
         <v>32</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="7">
-        <v>32</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
+      <c r="I4" s="6">
+        <v>32</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" s="8">
+        <v>32</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -870,8 +943,14 @@
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="37.5">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -893,21 +972,21 @@
       <c r="G5" s="4">
         <v>32</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="7">
-        <v>32</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="6">
+        <v>32</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="8">
+        <v>32</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
         <v>0</v>
       </c>
@@ -917,8 +996,14 @@
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="37.5">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -940,32 +1025,38 @@
       <c r="G6" s="4">
         <v>32</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="7">
-        <v>32</v>
-      </c>
-      <c r="J6">
+      <c r="I6" s="6">
+        <v>32</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="8">
+        <v>32</v>
+      </c>
+      <c r="L6">
         <v>2</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>3</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
       <c r="N6">
         <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>5</v>
       </c>
@@ -987,17 +1078,17 @@
       <c r="G7" s="4">
         <v>32</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="7">
-        <v>32</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
+      <c r="I7" s="6">
+        <v>32</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="8">
+        <v>32</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1011,8 +1102,14 @@
       <c r="O7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1034,32 +1131,38 @@
       <c r="G8" s="4">
         <v>32</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="7">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
+      <c r="I8" s="6">
+        <v>32</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="8">
+        <v>32</v>
       </c>
       <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>3</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
       <c r="O8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1081,17 +1184,17 @@
       <c r="G9" s="4">
         <v>32</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="7">
-        <v>32</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
+      <c r="I9" s="6">
+        <v>32</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="8">
+        <v>32</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1105,8 +1208,14 @@
       <c r="O9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1117,14 +1226,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
       <c r="L10">
         <v>0</v>
       </c>
@@ -1137,8 +1240,14 @@
       <c r="O10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1160,32 +1269,38 @@
       <c r="G11" s="5">
         <v>22</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="8">
-        <v>22</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
+      <c r="I11" s="7">
+        <v>22</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="9">
+        <v>22</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
         <v>1</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>38</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="37.5">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="56.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1207,17 +1322,17 @@
       <c r="G12" s="5">
         <v>22</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="8">
-        <v>22</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
+      <c r="I12" s="7">
+        <v>22</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="9">
+        <v>22</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1226,13 +1341,19 @@
         <v>0</v>
       </c>
       <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
         <v>43</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="51">
+    <row r="13" spans="1:17" ht="75">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1254,17 +1375,17 @@
       <c r="G13" s="5">
         <v>22</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I13" s="8">
-        <v>22</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
+      <c r="I13" s="7">
+        <v>22</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="9">
+        <v>22</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1273,13 +1394,19 @@
         <v>0</v>
       </c>
       <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>44</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1301,17 +1428,17 @@
       <c r="G14" s="5">
         <v>22</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="8">
-        <v>22</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
+      <c r="I14" s="7">
+        <v>22</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="9">
+        <v>22</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1320,13 +1447,19 @@
         <v>0</v>
       </c>
       <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
         <v>46</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="62.25">
+    <row r="15" spans="1:17" ht="93.75">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1348,17 +1481,17 @@
       <c r="G15" s="5">
         <v>22</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I15" s="8">
-        <v>22</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
+      <c r="I15" s="7">
+        <v>22</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="9">
+        <v>22</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1367,13 +1500,19 @@
         <v>0</v>
       </c>
       <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>47</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="47.25">
+    <row r="16" spans="1:17" ht="93.75">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1395,17 +1534,17 @@
       <c r="G16" s="5">
         <v>22</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="8">
-        <v>22</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
+      <c r="I16" s="7">
+        <v>22</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="9">
+        <v>22</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1417,10 +1556,16 @@
         <v>0</v>
       </c>
       <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:17">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1442,37 +1587,43 @@
       <c r="G17" s="5">
         <v>22</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="8">
-        <v>22</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
+      <c r="I17" s="7">
+        <v>22</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="9">
+        <v>22</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>2</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>49</v>
       </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:17">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1481,67 +1632,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:17">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:17">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:17">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:17">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:17">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:17">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:17">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:17">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:17">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:17">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:17">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:17">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:17">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81081E91-609E-4695-9AD5-B782AE314735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC89234-1EFE-411A-8D25-BD3FDA6BFE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -379,6 +379,55 @@
   </si>
   <si>
     <t>Finalizando el tutorial.</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Este é o mundo eterno.</t>
+  </si>
+  <si>
+    <t>É o mundo para onde vão aqueles que morrem no mundo dos vivos.</t>
+  </si>
+  <si>
+    <t>Me diga o nome que você usava no mundo dos vivos.</t>
+  </si>
+  <si>
+    <t>Digite um nome com no mínimo 2 e no máximo 10 caracteres.</t>
+  </si>
+  <si>
+    <t>Obrigado por me contar.</t>
+  </si>
+  <si>
+    <t>Muito bem, agora mesmo o seu nome...</t>
+  </si>
+  <si>
+    <t>Iniciando o tutorial.</t>
+  </si>
+  <si>
+    <t>Mova o personagem
+e clique com o botão esquerdo para abrir a gaveta.</t>
+  </si>
+  <si>
+    <t>Pressione P, Z ou ESC para abrir a tela de pausa → «Verificar itens»
+→ «Documento» → «Tutorial»</t>
+  </si>
+  <si>
+    <t>Clique esquerdo... abrir a gaveta.</t>
+  </si>
+  <si>
+    <t>Pressione P, Z ou ESC para abrir a tela de pausa → «Verificar itens»
+→ «Item Misterioso» → «Martelo» ou «Corda»</t>
+  </si>
+  <si>
+    <t>Clique esquerdo... tocar na Esfera Azul do Julgamento.
+Clique com o botão esquerdo na imagem do Item Misterioso para selecioná-lo.</t>
+  </si>
+  <si>
+    <t>Encerrando o tutorial.</t>
   </si>
 </sst>
 </file>
@@ -433,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -451,16 +500,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="114.5" customWidth="1"/>
@@ -751,15 +790,17 @@
     <col min="5" max="5" width="20.25" customWidth="1"/>
     <col min="6" max="6" width="38.125" customWidth="1"/>
     <col min="7" max="11" width="26.625" customWidth="1"/>
-    <col min="12" max="12" width="27.25" customWidth="1"/>
-    <col min="13" max="13" width="26.625" customWidth="1"/>
-    <col min="14" max="14" width="22.25" customWidth="1"/>
-    <col min="15" max="15" width="23.875" customWidth="1"/>
-    <col min="16" max="16" width="24.125" customWidth="1"/>
-    <col min="17" max="17" width="14.625" customWidth="1"/>
+    <col min="12" max="12" width="21.5" customWidth="1"/>
+    <col min="13" max="13" width="27.875" customWidth="1"/>
+    <col min="14" max="14" width="27.25" customWidth="1"/>
+    <col min="15" max="15" width="26.625" customWidth="1"/>
+    <col min="16" max="16" width="22.25" customWidth="1"/>
+    <col min="17" max="17" width="23.875" customWidth="1"/>
+    <col min="18" max="18" width="24.125" customWidth="1"/>
+    <col min="19" max="19" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -787,32 +828,38 @@
       <c r="I1" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" t="s">
         <v>72</v>
       </c>
       <c r="L1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" t="s">
         <v>1</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>2</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>3</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>4</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>0</v>
       </c>
@@ -823,14 +870,6 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
       <c r="N2">
         <v>0</v>
       </c>
@@ -843,8 +882,14 @@
       <c r="Q2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -872,17 +917,17 @@
       <c r="I3" s="6">
         <v>32</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K3" s="8">
-        <v>32</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="K3">
+        <v>32</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -896,8 +941,14 @@
       <c r="Q3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="56.25">
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="56.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -925,17 +976,17 @@
       <c r="I4" s="6">
         <v>32</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="8">
-        <v>32</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="K4">
+        <v>32</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -949,8 +1000,14 @@
       <c r="Q4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="37.5">
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -978,21 +1035,21 @@
       <c r="I5" s="6">
         <v>32</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="8">
-        <v>32</v>
-      </c>
-      <c r="L5">
+      <c r="K5">
+        <v>32</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5">
+        <v>32</v>
+      </c>
+      <c r="N5">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
@@ -1002,8 +1059,14 @@
       <c r="Q5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="37.5">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="37.5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1031,32 +1094,38 @@
       <c r="I6" s="6">
         <v>32</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="8">
-        <v>32</v>
-      </c>
-      <c r="L6">
+      <c r="K6">
+        <v>32</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6">
+        <v>32</v>
+      </c>
+      <c r="N6">
         <v>2</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1084,17 +1153,17 @@
       <c r="I7" s="6">
         <v>32</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="8">
-        <v>32</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="K7">
+        <v>32</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -1108,8 +1177,14 @@
       <c r="Q7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1137,32 +1212,38 @@
       <c r="I8" s="6">
         <v>32</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="8">
-        <v>32</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="K8">
+        <v>32</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>3</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
       <c r="Q8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1190,17 +1271,17 @@
       <c r="I9" s="6">
         <v>32</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="8">
-        <v>32</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="K9">
+        <v>32</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -1214,8 +1295,14 @@
       <c r="Q9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1226,14 +1313,6 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
       <c r="N10">
         <v>0</v>
       </c>
@@ -1246,8 +1325,14 @@
       <c r="Q10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1275,32 +1360,38 @@
       <c r="I11" s="7">
         <v>22</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K11" s="9">
-        <v>22</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
+      <c r="K11" s="1">
+        <v>22</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="1">
+        <v>22</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
         <v>1</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>38</v>
       </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="56.25">
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="75">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1328,17 +1419,17 @@
       <c r="I12" s="7">
         <v>22</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K12" s="9">
-        <v>22</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
+      <c r="K12" s="1">
+        <v>22</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="1">
+        <v>22</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1347,13 +1438,19 @@
         <v>0</v>
       </c>
       <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
         <v>43</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="75">
+    <row r="13" spans="1:19" ht="112.5">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1381,17 +1478,17 @@
       <c r="I13" s="7">
         <v>22</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="9">
-        <v>22</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
+      <c r="K13" s="1">
+        <v>22</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" s="1">
+        <v>22</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1400,13 +1497,19 @@
         <v>0</v>
       </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>44</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:19" ht="37.5">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1434,17 +1537,17 @@
       <c r="I14" s="7">
         <v>22</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K14" s="9">
-        <v>22</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
+      <c r="K14" s="1">
+        <v>22</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="1">
+        <v>22</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1453,13 +1556,19 @@
         <v>0</v>
       </c>
       <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
         <v>46</v>
       </c>
-      <c r="Q14">
+      <c r="S14">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="93.75">
+    <row r="15" spans="1:19" ht="112.5">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1487,17 +1596,17 @@
       <c r="I15" s="7">
         <v>22</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K15" s="9">
-        <v>22</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
+      <c r="K15" s="1">
+        <v>22</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="1">
+        <v>22</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1506,13 +1615,19 @@
         <v>0</v>
       </c>
       <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
         <v>47</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="93.75">
+    <row r="16" spans="1:19" ht="131.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1540,17 +1655,17 @@
       <c r="I16" s="7">
         <v>22</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K16" s="9">
-        <v>22</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
+      <c r="K16" s="1">
+        <v>22</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M16" s="1">
+        <v>22</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -1562,10 +1677,16 @@
         <v>0</v>
       </c>
       <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:19">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1593,37 +1714,43 @@
       <c r="I17" s="7">
         <v>22</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="9">
-        <v>22</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
+      <c r="K17" s="1">
+        <v>22</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M17" s="1">
+        <v>22</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
         <v>2</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>49</v>
       </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1632,67 +1759,67 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:19">
       <c r="A29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:19">
       <c r="A30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:19">
       <c r="A31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:19">
       <c r="A32">
         <v>30</v>
       </c>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC89234-1EFE-411A-8D25-BD3FDA6BFE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CADA9FF-AA59-44A8-810F-18A55B864BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CADA9FF-AA59-44A8-810F-18A55B864BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06277E49-4AC8-429E-B9A4-1A6CE3DA7C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -338,19 +338,7 @@
     <t>Este es el mundo eterno.</t>
   </si>
   <si>
-    <t>Es el mundo al que llegan quienes mueren en el mundo de los vivos.</t>
-  </si>
-  <si>
-    <t>Dime el nombre que usabas en el mundo de los vivos.</t>
-  </si>
-  <si>
-    <t>Introduce un nombre de entre 2 y 10 caracteres.</t>
-  </si>
-  <si>
     <t>Gracias por decírmelo.</t>
-  </si>
-  <si>
-    <t>Bien, ahora mismo tu nombre...</t>
   </si>
   <si>
     <t>será descartado.</t>
@@ -363,71 +351,97 @@
 y haz clic izquierdo para abrir el cajón.</t>
   </si>
   <si>
+    <t>Clic izquierdo... abrir el cajón.</t>
+  </si>
+  <si>
+    <t>Pulsa P, Z o ESC para abrir la pantalla de pausa → «Revisar objetos»
+→ «Objeto Misterioso» → «Martillo» o «Cuerda»</t>
+  </si>
+  <si>
+    <t>Clic izquierdo... tocar la Esfera Azul del Juicio.
+Haz clic izquierdo en la imagen del Objeto Misterioso para seleccionarlo.</t>
+  </si>
+  <si>
+    <t>Finalizando el tutorial.</t>
+  </si>
+  <si>
+    <t>messagePortuguese</t>
+  </si>
+  <si>
+    <t>messageSizePortuguese</t>
+  </si>
+  <si>
+    <t>Este é o mundo eterno.</t>
+  </si>
+  <si>
+    <t>É o mundo para onde vão aqueles que morrem no mundo dos vivos.</t>
+  </si>
+  <si>
+    <t>Me diga o nome que você usava no mundo dos vivos.</t>
+  </si>
+  <si>
+    <t>Iniciando o tutorial.</t>
+  </si>
+  <si>
+    <t>Clique esquerdo... abrir a gaveta.</t>
+  </si>
+  <si>
+    <t>Pressione P, Z ou ESC para abrir a tela de pausa → «Verificar itens»
+→ «Item Misterioso» → «Martelo» ou «Corda»</t>
+  </si>
+  <si>
+    <t>Clique esquerdo... tocar na Esfera Azul do Julgamento.
+Clique com o botão esquerdo na imagem do Item Misterioso para selecioná-lo.</t>
+  </si>
+  <si>
+    <t>Encerrando o tutorial.</t>
+  </si>
+  <si>
+    <t>Es el mundo al que llegan quienes mueren en el mundo de los vivos.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dime el nombre que usabas en el mundo de los vivos.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Introduce un nombre de entre 2 y 10 caracteres.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bien, ahora mismo tu nombre...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>será descartado.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Digite um nome com no mínimo 2 e no máximo 10 caracteres.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Muito bem, agora mesmo o seu nome...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Obrigado por me contar.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Pulsa P, Z o ESC para abrir la pantalla de pausa → «Revisar objetos»
 → «Documento» → «Tutorial»</t>
-  </si>
-  <si>
-    <t>Clic izquierdo... abrir el cajón.</t>
-  </si>
-  <si>
-    <t>Pulsa P, Z o ESC para abrir la pantalla de pausa → «Revisar objetos»
-→ «Objeto Misterioso» → «Martillo» o «Cuerda»</t>
-  </si>
-  <si>
-    <t>Clic izquierdo... tocar la Esfera Azul del Juicio.
-Haz clic izquierdo en la imagen del Objeto Misterioso para seleccionarlo.</t>
-  </si>
-  <si>
-    <t>Finalizando el tutorial.</t>
-  </si>
-  <si>
-    <t>messagePortuguese</t>
-  </si>
-  <si>
-    <t>messageSizePortuguese</t>
-  </si>
-  <si>
-    <t>Este é o mundo eterno.</t>
-  </si>
-  <si>
-    <t>É o mundo para onde vão aqueles que morrem no mundo dos vivos.</t>
-  </si>
-  <si>
-    <t>Me diga o nome que você usava no mundo dos vivos.</t>
-  </si>
-  <si>
-    <t>Digite um nome com no mínimo 2 e no máximo 10 caracteres.</t>
-  </si>
-  <si>
-    <t>Obrigado por me contar.</t>
-  </si>
-  <si>
-    <t>Muito bem, agora mesmo o seu nome...</t>
-  </si>
-  <si>
-    <t>Iniciando o tutorial.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pressione P, Z ou ESC para abrir a tela de pausa → «Verificar itens»
+→ «Documento» → «Tutorial»</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Mova o personagem
 e clique com o botão esquerdo para abrir a gaveta.</t>
-  </si>
-  <si>
-    <t>Pressione P, Z ou ESC para abrir a tela de pausa → «Verificar itens»
-→ «Documento» → «Tutorial»</t>
-  </si>
-  <si>
-    <t>Clique esquerdo... abrir a gaveta.</t>
-  </si>
-  <si>
-    <t>Pressione P, Z ou ESC para abrir a tela de pausa → «Verificar itens»
-→ «Item Misterioso» → «Martelo» ou «Corda»</t>
-  </si>
-  <si>
-    <t>Clique esquerdo... tocar na Esfera Azul do Julgamento.
-Clique com o botão esquerdo na imagem do Item Misterioso para selecioná-lo.</t>
-  </si>
-  <si>
-    <t>Encerrando o tutorial.</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -835,10 +849,10 @@
         <v>72</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
@@ -924,7 +938,7 @@
         <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="M3">
         <v>32</v>
@@ -977,16 +991,16 @@
         <v>32</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="K4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1036,16 +1050,16 @@
         <v>32</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="K5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="M5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -1095,16 +1109,16 @@
         <v>32</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="K6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -1154,13 +1168,13 @@
         <v>32</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -1213,13 +1227,13 @@
         <v>32</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="K8">
         <v>32</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M8">
         <v>32</v>
@@ -1272,13 +1286,13 @@
         <v>32</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="K9">
         <v>32</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M9">
         <v>32</v>
@@ -1361,13 +1375,13 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K11" s="1">
         <v>22</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="M11" s="1">
         <v>22</v>
@@ -1420,13 +1434,13 @@
         <v>22</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K12" s="1">
         <v>22</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M12" s="1">
         <v>22</v>
@@ -1479,13 +1493,13 @@
         <v>22</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K13" s="1">
         <v>22</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="M13" s="1">
         <v>22</v>
@@ -1538,13 +1552,13 @@
         <v>22</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K14" s="1">
         <v>22</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M14" s="1">
         <v>22</v>
@@ -1597,13 +1611,13 @@
         <v>22</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K15" s="1">
         <v>22</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="M15" s="1">
         <v>22</v>
@@ -1656,13 +1670,13 @@
         <v>22</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K16" s="1">
         <v>22</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M16" s="1">
         <v>22</v>
@@ -1715,13 +1729,13 @@
         <v>22</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K17" s="1">
         <v>22</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="M17" s="1">
         <v>22</v>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06277E49-4AC8-429E-B9A4-1A6CE3DA7C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2218C5B-28C0-4D71-9BE4-69EEFEA08D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,9 +221,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>这里是常世</t>
-  </si>
-  <si>
     <t>这是现世逝去之人最终到达的世界</t>
   </si>
   <si>
@@ -441,6 +438,10 @@
   <si>
     <t>Mova o personagem
 e clique com o botão esquerdo para abrir a gaveta.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>这里是常世</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -831,28 +832,28 @@
         <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" t="s">
-        <v>54</v>
-      </c>
       <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
         <v>69</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>70</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" t="s">
-        <v>72</v>
-      </c>
       <c r="L1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" t="s">
         <v>82</v>
-      </c>
-      <c r="M1" t="s">
-        <v>83</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
@@ -920,25 +921,25 @@
         <v>32</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="G3" s="4">
         <v>32</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" s="6">
         <v>32</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K3">
         <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M3">
         <v>32</v>
@@ -979,25 +980,25 @@
         <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" s="4">
         <v>32</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="6">
         <v>32</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K4">
         <v>24</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M4">
         <v>24</v>
@@ -1038,25 +1039,25 @@
         <v>32</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4">
         <v>32</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I5" s="6">
         <v>32</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K5">
         <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M5">
         <v>24</v>
@@ -1097,25 +1098,25 @@
         <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="4">
         <v>32</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I6" s="6">
         <v>32</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K6">
         <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M6">
         <v>24</v>
@@ -1156,25 +1157,25 @@
         <v>32</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4">
         <v>32</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I7" s="6">
         <v>32</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K7">
         <v>32</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M7">
         <v>32</v>
@@ -1215,25 +1216,25 @@
         <v>32</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="4">
         <v>32</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I8" s="6">
         <v>32</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K8">
         <v>32</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M8">
         <v>32</v>
@@ -1274,25 +1275,25 @@
         <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G9" s="4">
         <v>32</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9" s="6">
         <v>32</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>32</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M9">
         <v>32</v>
@@ -1363,25 +1364,25 @@
         <v>22</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G11" s="5">
         <v>22</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11" s="7">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K11" s="1">
         <v>22</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M11" s="1">
         <v>22</v>
@@ -1422,25 +1423,25 @@
         <v>22</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="5">
         <v>22</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" s="7">
         <v>22</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K12" s="1">
         <v>22</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M12" s="1">
         <v>22</v>
@@ -1481,25 +1482,25 @@
         <v>22</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="5">
         <v>22</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I13" s="7">
         <v>22</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="1">
+        <v>22</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="K13" s="1">
-        <v>22</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="M13" s="1">
         <v>22</v>
@@ -1540,25 +1541,25 @@
         <v>22</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" s="5">
         <v>22</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" s="7">
         <v>22</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K14" s="1">
         <v>22</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M14" s="1">
         <v>22</v>
@@ -1599,25 +1600,25 @@
         <v>22</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" s="5">
         <v>22</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I15" s="7">
         <v>22</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K15" s="1">
         <v>22</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M15" s="1">
         <v>22</v>
@@ -1658,25 +1659,25 @@
         <v>22</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G16" s="5">
         <v>22</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I16" s="7">
         <v>22</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K16" s="1">
         <v>22</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M16" s="1">
         <v>22</v>
@@ -1717,25 +1718,25 @@
         <v>22</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="5">
         <v>22</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I17" s="7">
         <v>22</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K17" s="1">
         <v>22</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M17" s="1">
         <v>22</v>

--- a/Assets/Originals/Excels/System/SystemMessage.xlsx
+++ b/Assets/Originals/Excels/System/SystemMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2218C5B-28C0-4D71-9BE4-69EEFEA08D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8207965-25A2-4A24-93E6-2FB6C69D9E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1764,6 +1764,18 @@
       <c r="A18">
         <v>16</v>
       </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19">
